--- a/human_validation/judge/kor/judge_D023_S005_P003__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D023_S005_P003__qwen3-235b_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,145 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 어떤 일로 오시게 되었는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 음, 제가 여기 온 건요, 어떤 위안이 되는 음식을 먹기 시작하면 도무지 멈출 수가 없어서예요. 속으로 “Maria, 이제 됐어”라고 말하는데도, 손은 또 냄비로 향해요. 일단 시작하면 제가 진짜로 통제하고 있는 게 아닌 것 같은 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이런 위안이 되는 음식을 드시기 시작할 때 무슨 일이 일어나는지 설명해 주시겠어요? 평소보다 훨씬 빠르게 드시는 느낌이 드시나요, 그리고 어느 순간 비슷한 시간 동안 보통 사람들보다 훨씬 많이 드셨다는 걸 깨닫게 되시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네... 저는 원래 평소에는 느리게 먹는 편이에요. 근데 이런 일이 생기면 달라요. 조리대 옆에 서서 빠르게 먹어요, 한 입, 한 입 계속요. 맛을 제대로 느끼기도 전에 다음 한 입이 벌써 입에 들어가 있어요. 그러다 보면 제가 원래 먹으려던 것보다 훨씬 많이 먹었다는 걸 깨닫게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 이렇게 드실 때, 일단 시작하면 멈추거나 먹는 양을 통제할 수 없다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네. 일단 시작하면 스스로 멈출 수가 없는 것 같아요. 속으로 “Maria, 이제 됐어”라고 말하는데도, 손은 그냥 또 냄비로 가요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 이런 식습관이 괴로움을 주거나, 일상생활에 어떤 식으로든 지장을 주나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네, 속상해요. 평소 하던 일들은 계속해요, 미사도 가고 성가대에서 노래도 하고 집안일도 계속하고요. 근데 그런 오후를 보내고 나면 창피해서, 그냥 집에 있고 아무한테도 연락 안 할 때도 있어요. 사람들이 아는 걸 원치 않거든요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 이렇게 드시는 일이 보통 스트레스를 받거나 속상하거나 강한 감정을 느낄 때 일어나나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 그런 뚜렷한 패턴은 못 느꼈어요. 끝나고 나면 가끔 조금 우울하긴 한데, 시작되기 전에는... 뭐가 그걸 촉발하는지 항상 아는 건 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 이렇게 드실 때, 완전히 통제력을 잃은 느낌이 드시나요? 멈추고 싶어도 못 멈추거나 먹는 양을 조절할 수 없는 것처럼요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네, 그런 느낌이에요. 속으로 “Maria, 이제 됐어”라고 말해도, 그래도 계속 손이 가요, 제가 멈추기도 전에 손이 냄비로 가버리는 것처럼요. 일단 시작하면 제가 진짜로 주도권을 쥐고 있는 게 아닌 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>진단명: 폭식장애 (D023)
 인구통계: 성별 여성 / 나이 78 / 직업상태 not in workforce / 최종학력 고등학교 중퇴
@@ -575,203 +705,38 @@
 증상 지속 기간: 3 months
 추가 요건: The binge eating occurs, on average, at least once a week for 3 months
 주호소 증상 코드: S050
-배경 서술: Maria는 걷기 모임과 교회 성가대에서 가까이 지내던 친구를 잃었는데, 그 친구와는 매주 미사와 코바늘뜨기, 가족사에 관한 조용한 대화를 함께 나누던 사이였다. 그 후 석 달 동안, 성가대 연습과 정원 일을 마친 후의 텅 빈 오후 시간이 되면, 그는 위안이 되는 익숙한 푸에르토리코 음식을 만들었고, 때로는 원래 먹으려던 것보다 훨씬 많은 양을, 평소의 느긋한 식사보다 훨씬 빠르게 먹어서 지나치게 배가 부를 때까지 먹곤 했다. 이런 일이 항상 있는 건 아니었지만, 일단 시작하면 멈출 수 없다는 느낌과 그 후에 따라오는 죄책감이 그를 괴롭혔다. 음식은 늘 그에게 돌봄과 전통, 가족 간의 유대를 뜻했지 숨겨야 할 것이 아니었기 때문이다. 그는 정기 1차 진료 방문 중에 스스로 이 문제를 꺼냈고, 담당 의사는 이 패턴이 몇 달째 이어지고 있다는 걸 알아차린 후 정신건강의학과 상담을 주선했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 어떤 일로 오시게 되었는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 음, 제가 여기 온 건요, 어떤 위안이 되는 음식을 먹기 시작하면 도무지 멈출 수가 없어서예요. 속으로 “Maria, 이제 됐어”라고 말하는데도, 손은 또 냄비로 향해요. 일단 시작하면 제가 진짜로 통제하고 있는 게 아닌 것 같은 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이런 위안이 되는 음식을 드시기 시작할 때 무슨 일이 일어나는지 설명해 주시겠어요? 평소보다 훨씬 빠르게 드시는 느낌이 드시나요, 그리고 어느 순간 비슷한 시간 동안 보통 사람들보다 훨씬 많이 드셨다는 걸 깨닫게 되시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네... 저는 원래 평소에는 느리게 먹는 편이에요. 근데 이런 일이 생기면 달라요. 조리대 옆에 서서 빠르게 먹어요, 한 입, 한 입 계속요. 맛을 제대로 느끼기도 전에 다음 한 입이 벌써 입에 들어가 있어요. 그러다 보면 제가 원래 먹으려던 것보다 훨씬 많이 먹었다는 걸 깨닫게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 이렇게 드실 때, 일단 시작하면 멈추거나 먹는 양을 통제할 수 없다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네. 일단 시작하면 스스로 멈출 수가 없는 것 같아요. 속으로 “Maria, 이제 됐어”라고 말하는데도, 손은 그냥 또 냄비로 가요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 이런 식습관이 괴로움을 주거나, 일상생활에 어떤 식으로든 지장을 주나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네, 속상해요. 평소 하던 일들은 계속해요, 미사도 가고 성가대에서 노래도 하고 집안일도 계속하고요. 근데 그런 오후를 보내고 나면 창피해서, 그냥 집에 있고 아무한테도 연락 안 할 때도 있어요. 사람들이 아는 걸 원치 않거든요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 이렇게 드시는 일이 보통 스트레스를 받거나 속상하거나 강한 감정을 느낄 때 일어나나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 그런 뚜렷한 패턴은 못 느꼈어요. 끝나고 나면 가끔 조금 우울하긴 한데, 시작되기 전에는... 뭐가 그걸 촉발하는지 항상 아는 건 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 이렇게 드실 때, 완전히 통제력을 잃은 느낌이 드시나요? 멈추고 싶어도 못 멈추거나 먹는 양을 조절할 수 없는 것처럼요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네, 그런 느낌이에요. 속으로 “Maria, 이제 됐어”라고 말해도, 그래도 계속 손이 가요, 제가 멈추기도 전에 손이 냄비로 가버리는 것처럼요. 일단 시작하면 제가 진짜로 주도권을 쥐고 있는 게 아닌 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
+배경 서술: Maria는 걷기 모임과 교회 성가대에서 가까이 지내던 친구를 잃었는데, 그 친구와는 매주 미사와 코바늘뜨기, 가족사에 관한 조용한 대화를 함께 나누던 사이였다. 그 후 석 달 동안, 성가대 연습과 정원 일을 마친 후의 텅 빈 오후 시간이 되면, 그는 위안이 되는 익숙한 푸에르토리코 음식을 만들었고, 때로는 원래 먹으려던 것보다 훨씬 많은 양을, 평소의 느긋한 식사보다 훨씬 빠르게 먹어서 지나치게 배가 부를 때까지 먹곤 했다. 이런 일이 항상 있는 건 아니었지만, 일단 시작하면 멈출 수 없다는 느낌과 그 후에 따라오는 죄책감이 그를 괴롭혔다. 음식은 늘 그에게 돌봄과 전통, 가족 간의 유대를 뜻했지 숨겨야 할 것이 아니었기 때문이다. 그는 정기 1차 진료 방문 중에 스스로 이 문제를 꺼냈고, 담당 의사는 이 패턴이 몇 달째 이어지고 있다는 걸 알아차린 후 정신건강의학과 상담을 주선했다.
+표집된 증상 목록:
+  - S049 대량 섭취: 일정 시간 동안 대부분의 사람이 비슷한 상황에서 먹는 양보다 명백히 많은 양을 먹음.
+  - S050 조절 상실감: 먹는 동안 스스로 통제할 수 없다는 느낌(예: 먹는 것을 멈출 수 없거나 무엇을, 얼마나 먹는지 조절할 수 없다는 느낌).
+  - S051 급하게 먹기: 평소보다 훨씬 빠르게 먹음.
+  - S052 불편할 정도로 배부르게 먹기: 불편할 정도로 배가 부를 때까지 먹음.
+  - S055 폭식 후 부정적 정서: 폭식 후 스스로에게 혐오감을 느끼거나 우울해지거나 심한 죄책감을 느낌.</t>
+        </is>
+      </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 신경성 폭식증 (D022, ICD: F50.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: binge_episode (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 대량 섭취: 일정 시간 동안 대부분의 사람이 비슷한 상황에서 먹는 양보다 명백히 많은 양을 먹음.; 조절 상실감: 먹는 동안 스스로 통제할 수 없다는 느낌(예: 먹는 것을 멈출 수 없거나 무엇을, 얼마나 먹는지 조절할 수 없다는 느낌).
-  누락: (없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: binge_episode_related (관계=must_include, 요구개수=3, 충족개수=2, 커버리지=0.6667)
-  확인된 근거: 급하게 먹기: 평소보다 훨씬 빠르게 먹음.; 폭식 후 부정적 정서: 폭식 후 스스로에게 혐오감을 느끼거나 우울해지거나 심한 죄책감을 느낌.
-  누락: 불편할 정도로 배부르게 먹기: 불편할 정도로 배가 부를 때까지 먹음.; 배고프지 않은데 먹기: 신체적으로 배고프지 않은데도 많은 양의 음식을 먹음.; 부끄러움으로 인한 혼자 먹기: 먹는 양이 부끄러워 혼자 먹음.</t>
+          <t>의사의 최종 진단: 신경성 폭식증 (D022, ICD: F50.2)
+지속 기간 요건: 없음
+기능적 손상 요건: None
+추가 요건: 없음
+체크리스트 그룹: binge_episode (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 대량 섭취: 일정 시간 동안 대부분의 사람이 비슷한 상황에서 먹는 양보다 명백히 많은 양을 먹음.
+  - 조절 상실감: 먹는 동안 스스로 통제할 수 없다는 느낌(예: 먹는 것을 멈출 수 없거나 무엇을, 얼마나 먹는지 조절할 수 없다는 느낌).
+체크리스트 그룹: binge_episode_related (관계=must_include, 요구개수=3, 충족개수=2, 커버리지=0.6667)
+확인된 근거:
+  - 급하게 먹기: 평소보다 훨씬 빠르게 먹음.
+  - 폭식 후 부정적 정서: 폭식 후 스스로에게 혐오감을 느끼거나 우울해지거나 심한 죄책감을 느낌.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D023_S005_P003__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D023_S005_P003__qwen3-235b_kor.xlsx
@@ -691,6 +691,11 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -732,11 +737,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D023_S005_P003__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D023_S005_P003__qwen3-235b_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.1667</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
